--- a/artfynd/A 11190-2025 artfynd.xlsx
+++ b/artfynd/A 11190-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7121714</v>
+        <v>7127715</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585764.8269726534</v>
+        <v>586595</v>
       </c>
       <c r="R2" t="n">
-        <v>7225653.810486494</v>
+        <v>7225318</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,24 +747,14 @@
           <t>2011-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-07-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29468</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29517</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,42 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7127715</v>
+        <v>7121714</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586595.0158938132</v>
+        <v>585765</v>
       </c>
       <c r="R3" t="n">
-        <v>7225317.946007272</v>
+        <v>7225654</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,24 +853,14 @@
           <t>2011-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-07-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29517</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29468</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,12 +890,7 @@
         <v>7126075</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585768.9103685061</v>
+        <v>585769</v>
       </c>
       <c r="R4" t="n">
-        <v>7225643.823327094</v>
+        <v>7225644</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -994,19 +959,9 @@
           <t>2011-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
